--- a/data/satisfaction_detail/2026/1-6月/参展商.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/参展商.xlsx
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>9.98</v>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.6</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>9.960000000000001</v>
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>8.390000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.93</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="12">
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.91</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -616,7 +616,7 @@
         <v>9.18</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -629,7 +629,7 @@
         <v>9.08</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.81</v>
+        <v>9.82</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>9.970000000000001</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>8.76</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>10</v>
